--- a/Python/dz2/work/data/db.xlsx
+++ b/Python/dz2/work/data/db.xlsx
@@ -512,12 +512,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.57" customWidth="1" min="1" max="1"/>
-    <col width="15.85" customWidth="1" min="2" max="2"/>
-    <col width="12.94" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -579,15 +579,105 @@
       <c r="C4" s="6" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Собака</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Кошка</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Сиамская</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Кошка</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Британская короткошерстная</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Собака</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Овчарка</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Собака</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Такса</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Собака</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Хаски</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Кошка</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Мейн-кун</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -600,16 +690,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.57" customWidth="1" min="1" max="1"/>
-    <col width="15.85" customWidth="1" min="2" max="2"/>
-    <col width="12.94" customWidth="1" min="3" max="3"/>
-    <col width="17.28" customWidth="1" min="4" max="4"/>
-    <col width="20.53" customWidth="1" min="5" max="5"/>
-    <col width="20.97" customWidth="1" min="6" max="6"/>
-    <col width="39.61" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -658,7 +748,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -678,7 +768,139 @@
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>Передана по договору пристройства</t>
+          <t>Передача оформлена по договору</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Егоров Павел</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>+7-902-111-11-11</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>egorov@example.com</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Передача оформлена по договору</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Васильева Ирина</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>+7-902-222-22-22</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>vasileva@example.com</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Передача оформлена по договору</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Ковалев Андрей</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>+7-902-333-33-33</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>kovalev@example.com</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Передача оформлена по договору</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Романова Алиса</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>+7-902-444-44-44</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>romanova@example.com</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Передача оформлена по договору</t>
         </is>
       </c>
     </row>
@@ -693,11 +915,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.57" customWidth="1" min="1" max="1"/>
-    <col width="15.85" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -733,12 +955,32 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Пристроено</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Карантин</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Готов к пристройству</t>
         </is>
       </c>
     </row>
@@ -753,22 +995,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.57" customWidth="1" min="1" max="1"/>
-    <col width="15.85" customWidth="1" min="2" max="2"/>
-    <col width="12.94" customWidth="1" min="3" max="3"/>
-    <col width="17.28" customWidth="1" min="4" max="4"/>
-    <col width="20.53" customWidth="1" min="5" max="5"/>
-    <col width="20.97" customWidth="1" min="6" max="6"/>
-    <col width="39.61" customWidth="1" min="7" max="7"/>
-    <col width="8.609999999999999" customWidth="1" min="8" max="8"/>
-    <col width="31.7" customWidth="1" min="9" max="9"/>
-    <col width="8.49" customWidth="1" min="10" max="10"/>
-    <col width="10.02" customWidth="1" min="11" max="11"/>
-    <col width="11.75" customWidth="1" min="12" max="12"/>
-    <col width="37.34" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -891,7 +1133,7 @@
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>Спокойная, хорошо контактирует с людьми</t>
+          <t>Ready for regular care</t>
         </is>
       </c>
     </row>
@@ -936,76 +1178,2185 @@
         </is>
       </c>
       <c r="J3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>900002</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>A-003</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Луна</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Чёрная</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>900002</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>Нужен курс лечения и повторный осмотр</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="7" t="n">
+      <c r="K4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>900003</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Adopted by a new family</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>A-004</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Рекс</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-02</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Чепрачный</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>900004</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>A-005</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Сима</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Кремовая</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>900005</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>A-006</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Барсик</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>A-003</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Луна</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="n">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Серый</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>900006</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>A-007</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Джек</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>2019-06-30</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Палевый</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>900007</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>A-008</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Ася</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>2021-12-12</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Голубая</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>900008</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>A-009</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Тайга</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>2023-01-03</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Серо-белая</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>900009</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>A-010</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Марс</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2020-04-24</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Коричневый</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>900010</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>A-011</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Нора</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Трёхцветная</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>900011</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>A-012</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Граф</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Чёрно-рыжий</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>900012</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>A-013</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Марта</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Белая</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>900013</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>A-014</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Чарли</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>2021-07-19</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Пятнистый</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>900014</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>A-015</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Кира</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>2020-12-29</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Шоколадная</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>900015</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Adopted by a new family</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>A-016</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Том</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>2023-03-16</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Полосатый</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>900016</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>A-017</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Боня</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="n">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>2019-09-12</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Палевая</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>900017</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>A-018</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Рыжик</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>Чёрная</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>900003</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>Пристроена в новую семью</t>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>2024-01-30</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Рыжий</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>900018</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>A-019</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Шерри</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2022-06-07</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Рыже-белая</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>900019</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>A-020</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Оскар</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>2021-02-14</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Дымчатый</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>900020</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>A-021</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Мила</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Серая</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>900021</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>A-022</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Пират</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>2020-01-05</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Серо-чёрный</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>900022</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>Adopted by a new family</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>A-023</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Злата</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>2022-04-04</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Золотистая</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>900023</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>A-024</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Бакс</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>2021-08-08</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Чёрный</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>900024</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>A-025</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Соня</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Кремовая</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>900025</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>A-026</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Лорд</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Палевый</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>900026</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>A-027</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Фрося</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2020-10-10</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Черепаховая</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>900027</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>A-028</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Спайк</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>2022-12-03</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Коричневый</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>900028</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>A-029</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Моника</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>2021-05-22</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Голубая</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>900029</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>Adopted by a new family</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>A-030</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Снежок</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Белый</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>900030</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>A-031</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Веста</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>2020-03-03</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Серо-белая</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>900031</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>A-032</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Кузя</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Полосатый</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>900032</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>A-033</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Дина</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Белая с пятнами</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>900033</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>A-034</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Арчи</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>2022-02-22</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Чепрачный</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>900034</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>A-035</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Лея</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Серая</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>900035</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>A-036</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Тиша</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>2020-07-07</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Кремовый</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>900036</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>Adopted by a new family</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>A-037</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Гера</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>2019-02-09</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Палевая</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>900037</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>A-038</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Феликс</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>2021-04-13</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Дымчатый</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>900038</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>Requires observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>A-039</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Рада</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>2023-08-23</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Рыжая</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>900039</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>A-040</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Макс</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Серо-белый</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>900040</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>Ready for regular care</t>
         </is>
       </c>
     </row>
@@ -1020,18 +3371,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.57" customWidth="1" min="1" max="1"/>
-    <col width="15.85" customWidth="1" min="2" max="2"/>
-    <col width="12.94" customWidth="1" min="3" max="3"/>
-    <col width="17.28" customWidth="1" min="4" max="4"/>
-    <col width="20.53" customWidth="1" min="5" max="5"/>
-    <col width="20.97" customWidth="1" min="6" max="6"/>
-    <col width="39.61" customWidth="1" min="7" max="7"/>
-    <col width="8.609999999999999" customWidth="1" min="8" max="8"/>
-    <col width="31.7" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1125,45 +3476,389 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Петрова</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Анна</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Олеговна</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>+7-900-222-22-22</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>petrova@example.com</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="H3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>Помогает с кормлением и лечением</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Соколова</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Игоревна</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+7-900-444-44-44</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>sokolova@example.com</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Социализация кошек</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Кузнецов</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Дмитрий</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Павлович</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>+7-900-555-55-55</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>kuznetsov@example.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Перевозка животных</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Орлова</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Елена</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Викторовна</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+7-900-666-66-66</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>orlova@example.com</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Помощь на приемах ветеринара</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Морозов</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Артем</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Андреевич</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+7-900-777-77-77</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>morozov@example.com</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Выгул активных собак</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Федорова</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Ольга</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Николаевна</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+7-900-888-88-88</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>fedorova@example.com</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Фото и анкеты животных</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Алексеев</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Петр</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Романович</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>+7-900-999-99-99</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>alekseev@example.com</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Кормление и уборка</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Никитина</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Дарья</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Михайловна</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>+7-901-111-11-11</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>nikitina@example.com</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Помощь с лечением</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Громов</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Максим</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Юрьевич</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>+7-901-222-22-22</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>gromov@example.com</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Временно не участвует</t>
         </is>
       </c>
     </row>
@@ -1178,11 +3873,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.57" customWidth="1" min="1" max="1"/>
-    <col width="15.85" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1218,12 +3913,32 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Лечение</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
         </is>
       </c>
     </row>
@@ -1238,14 +3953,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.57" customWidth="1" min="1" max="1"/>
-    <col width="15.85" customWidth="1" min="2" max="2"/>
-    <col width="12.94" customWidth="1" min="3" max="3"/>
-    <col width="17.28" customWidth="1" min="4" max="4"/>
-    <col width="20.53" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1287,7 +4002,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E2" s="6" t="n"/>
@@ -1297,34 +4012,331 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E3" s="6" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1337,16 +4349,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.57" customWidth="1" min="1" max="1"/>
-    <col width="15.85" customWidth="1" min="2" max="2"/>
-    <col width="12.94" customWidth="1" min="3" max="3"/>
-    <col width="17.28" customWidth="1" min="4" max="4"/>
-    <col width="20.53" customWidth="1" min="5" max="5"/>
-    <col width="20.97" customWidth="1" min="6" max="6"/>
-    <col width="39.61" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1391,27 +4403,2318 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="B3" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Лечение</t>
         </is>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F13" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>Обработка кожи и контроль состояния</t>
+      <c r="B46" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C48" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="C52" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C56" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C59" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C60" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C65" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C66" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C67" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C68" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C71" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C72" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Кормление</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>Кормление: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Лечение</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>Лечение: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>Социализация</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>Социализация: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>Перевозка</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>Перевозка: плановая работа</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>Выгул</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>Выгул: плановая работа</t>
         </is>
       </c>
     </row>
@@ -1426,14 +6729,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.57" customWidth="1" min="1" max="1"/>
-    <col width="15.85" customWidth="1" min="2" max="2"/>
-    <col width="12.94" customWidth="1" min="3" max="3"/>
-    <col width="17.28" customWidth="1" min="4" max="4"/>
-    <col width="20.53" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1480,7 +6783,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Поступила в приют</t>
+          <t>Поступление в приют</t>
         </is>
       </c>
     </row>
@@ -1501,7 +6804,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Поступил в приют</t>
+          <t>Поступление в приют</t>
         </is>
       </c>
     </row>
@@ -1517,12 +6820,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Переведён на лечение</t>
+          <t>Назначен дополнительный контроль</t>
         </is>
       </c>
     </row>
@@ -1543,28 +6846,1267 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Поступила в приют</t>
+          <t>Поступление в приют</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Передан новому владельцу</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Готов к пристройству</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Назначен дополнительный контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Назначен дополнительный контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Готов к пристройству</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Назначен дополнительный контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Назначен дополнительный контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Передан новому владельцу</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Готов к пристройству</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Готов к пристройству</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Пристроена</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Назначен дополнительный контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Передан новому владельцу</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Готов к пристройству</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Назначен дополнительный контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Назначен дополнительный контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Готов к пристройству</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Передан новому владельцу</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Назначен дополнительный контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Назначен дополнительный контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Готов к пристройству</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Передан новому владельцу</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Назначен дополнительный контроль</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Готов к пристройству</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Поступление в приют</t>
         </is>
       </c>
     </row>
@@ -1579,16 +8121,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.57" customWidth="1" min="1" max="1"/>
-    <col width="15.85" customWidth="1" min="2" max="2"/>
-    <col width="12.94" customWidth="1" min="3" max="3"/>
-    <col width="17.28" customWidth="1" min="4" max="4"/>
-    <col width="20.53" customWidth="1" min="5" max="5"/>
-    <col width="20.97" customWidth="1" min="6" max="6"/>
-    <col width="39.61" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -1633,64 +8175,988 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Дерматит</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Обработка и мазь</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Сергеев А.А.</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Контроль через 10 дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="B3" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Вакцинация</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Плановая вакцинация</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Ильина Н.В.</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Побочных реакций нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Отит</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Капли и чистка ушей</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Сергеев А.А.</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Назначен повторный прием</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Истощение</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Диета и витамины</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Кузьмина Е.С.</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Нужен контроль веса</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Травма лапы</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Перевязка и покой</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Кузьмина Е.С.</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Ограничить активность</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Первичный осмотр</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Лечение не требуется</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Ильина Н.В.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Общее состояние удовлетворительное</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Дерматит</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Обработка и мазь</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Сергеев А.А.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>Наблюдается улучшение</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-13</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Контроль через 10 дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Вакцинация</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Плановая вакцинация</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Ильина Н.В.</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Побочных реакций нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Отит</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Капли и чистка ушей</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Сергеев А.А.</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Назначен повторный прием</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Истощение</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Диета и витамины</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Кузьмина Е.С.</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Нужен контроль веса</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Травма лапы</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Перевязка и покой</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Кузьмина Е.С.</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Ограничить активность</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Первичный осмотр</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Лечение не требуется</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Ильина Н.В.</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>Общее состояние хорошее</t>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Общее состояние удовлетворительное</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Дерматит</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Обработка и мазь</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Сергеев А.А.</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Контроль через 10 дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Вакцинация</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Плановая вакцинация</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Ильина Н.В.</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Побочных реакций нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Отит</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Капли и чистка ушей</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Сергеев А.А.</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Назначен повторный прием</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Истощение</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Диета и витамины</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Кузьмина Е.С.</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Нужен контроль веса</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Травма лапы</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Перевязка и покой</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Кузьмина Е.С.</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Ограничить активность</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Первичный осмотр</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Лечение не требуется</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Ильина Н.В.</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Общее состояние удовлетворительное</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Дерматит</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Обработка и мазь</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Сергеев А.А.</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Контроль через 10 дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Вакцинация</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Плановая вакцинация</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Ильина Н.В.</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Побочных реакций нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Отит</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Капли и чистка ушей</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Сергеев А.А.</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Назначен повторный прием</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Истощение</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Диета и витамины</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Кузьмина Е.С.</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Нужен контроль веса</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Травма лапы</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Перевязка и покой</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Кузьмина Е.С.</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Ограничить активность</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Первичный осмотр</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Лечение не требуется</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Ильина Н.В.</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Общее состояние удовлетворительное</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Дерматит</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Обработка и мазь</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Сергеев А.А.</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Контроль через 10 дней</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Вакцинация</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Плановая вакцинация</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Ильина Н.В.</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Побочных реакций нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Отит</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Капли и чистка ушей</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Сергеев А.А.</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Назначен повторный прием</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Истощение</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Диета и витамины</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Кузьмина Е.С.</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Нужен контроль веса</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Травма лапы</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Перевязка и покой</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Кузьмина Е.С.</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Ограничить активность</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Первичный осмотр</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Лечение не требуется</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Ильина Н.В.</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Общее состояние удовлетворительное</t>
         </is>
       </c>
     </row>
